--- a/output/pdf_financials_xlsx/TRZ.xlsx
+++ b/output/pdf_financials_xlsx/TRZ.xlsx
@@ -7150,49 +7150,49 @@
         <v>9.09</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>11.063</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>13.336</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>15.391</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>15.444</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>17.105</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>17.849</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>17.817</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>18.017</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>15.948</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>15.948</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>15.948</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>16.092</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>16.329</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>0</v>
+        <v>16.283</v>
       </c>
       <c r="U92" s="3" t="n">
-        <v>0</v>
+        <v>16.454</v>
       </c>
     </row>
     <row r="93">
@@ -14100,7 +14100,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -35332,7 +35336,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TRZ.xlsx
+++ b/output/pdf_financials_xlsx/TRZ.xlsx
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-4.588</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-3.036</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>61.847</v>
+        <v>66.435</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>65.607</v>
+        <v>68.643</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-17.427</v>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>61.847</v>
+        <v>66.435</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>65.607</v>
+        <v>68.643</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>26.387</v>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1.744458431502075</v>
+        <v>1.873867704122114</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1.875087349455268</v>
+        <v>1.961858047596415</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>0.722107117709727</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>0</v>
+        <v>24.576</v>
       </c>
       <c r="F69" s="3" t="n">
         <v>13.768</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>24.576</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>13.768</v>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>344.309</v>
+        <v>319.733</v>
       </c>
       <c r="F75" s="3" t="n">
         <v>363.498</v>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>24.576</v>
+        <v>0</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>13.768</v>
+        <v>0</v>
       </c>
       <c r="G77" s="3" t="n">
         <v>0</v>
@@ -6161,10 +6161,10 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>24.576</v>
+        <v>0</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>13.768</v>
+        <v>0</v>
       </c>
       <c r="G79" s="3" t="n">
         <v>0</v>
@@ -6237,7 +6237,7 @@
         <v>0.06689877259698226</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.06817495333026329</v>
+        <v>0.03408747666513164</v>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>97.893</v>
+        <v>111.661</v>
       </c>
       <c r="G85" s="3" t="n">
         <v>79.934</v>
@@ -50512,7 +50512,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -92082,7 +92082,7 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">

--- a/output/pdf_financials_xlsx/TRZ.xlsx
+++ b/output/pdf_financials_xlsx/TRZ.xlsx
@@ -1486,10 +1486,10 @@
         <v>-16.95</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>138.667</v>
+        <v>141.914</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>52.699</v>
+        <v>55.89</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>108.696</v>
@@ -1498,7 +1498,7 @@
         <v>-134.133</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>286.112</v>
+        <v>290.176</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>15.037</v>
@@ -1846,10 +1846,10 @@
         <v>-13.536</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>57.955</v>
+        <v>61.202</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>22.875</v>
+        <v>26.066</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>49.319</v>
@@ -2065,10 +2065,10 @@
         <v>-13.536</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>57.955</v>
+        <v>61.202</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>22.875</v>
+        <v>26.066</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>46.964</v>
@@ -2077,7 +2077,7 @@
         <v>-36.759</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>134.308</v>
+        <v>138.372</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>9.993</v>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>36.999449</v>
+        <v>38.119008</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>58.782353</v>
@@ -2405,10 +2405,10 @@
         <v>-16.95</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>138.667</v>
+        <v>141.914</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>52.699</v>
+        <v>55.89</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>108.696</v>
@@ -2417,7 +2417,7 @@
         <v>-134.133</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>286.112</v>
+        <v>290.176</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>15.037</v>
@@ -2551,10 +2551,10 @@
         <v>23.843</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>177.735</v>
+        <v>180.982</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>99.401</v>
+        <v>102.592</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>154.513</v>
@@ -2563,7 +2563,7 @@
         <v>-84.095</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>354.582</v>
+        <v>358.646</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>74.16200000000001</v>
@@ -2624,10 +2624,10 @@
         <v>0.6419384532791417</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>4.871910701236075</v>
+        <v>4.960914521794287</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2.649140583732521</v>
+        <v>2.734184070243628</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>5.331803516278748</v>
@@ -2636,7 +2636,7 @@
         <v>-2.910218068233963</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>11.79837922102121</v>
+        <v>11.93360496049538</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>2.603129919566999</v>
@@ -2697,10 +2697,10 @@
         <v>-100</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>58.20562931339107</v>
+        <v>56.87388136477022</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>56.59310423347692</v>
+        <v>53.36196099481124</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>56.79325826157356</v>
@@ -2709,7 +2709,7 @@
         <v>-72.59511082284001</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>53.05754389889275</v>
+        <v>52.31445743273048</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>33.54392498503691</v>
@@ -2770,10 +2770,10 @@
         <v>-0.364437315085621</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1.588609923144776</v>
+        <v>1.677613743702987</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.609642668110798</v>
+        <v>0.6946861546219043</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>1.620593868079159</v>
@@ -2782,7 +2782,7 @@
         <v>-1.272093536716954</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>4.468971116460839</v>
+        <v>4.604196855935009</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>0.3507601910174081</v>
@@ -82726,11 +82726,7 @@
           <t>Shareholders</t>
         </is>
       </c>
-      <c r="D645" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+      <c r="D645" t="inlineStr"/>
       <c r="E645" t="inlineStr">
         <is>
           <t>-</t>
